--- a/docs/PRAP_NewApp_Specification_v1.3.xlsx
+++ b/docs/PRAP_NewApp_Specification_v1.3.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PRAP_NewApp_Development_Plan_v1.9.xlsx - the approved baseline, Gate N1 closed 2026-08-13</t>
+          <t>PRAP_NewApp_Development_Plan_v1.10.xlsx - the approved baseline, Gate N1 closed 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>The NR-ids are READ from PRAP_NewApp_Development_Plan_v1.9.xlsx when this workbook is generated, not re-typed. A requirement cannot be dropped between the two documents without this sheet showing it.</t>
+          <t>The NR-ids are READ from PRAP_NewApp_Development_Plan_v1.10.xlsx when this workbook is generated, not re-typed. A requirement cannot be dropped between the two documents without this sheet showing it.</t>
         </is>
       </c>
     </row>

--- a/docs/PRAP_NewApp_Specification_v1.3.xlsx
+++ b/docs/PRAP_NewApp_Specification_v1.3.xlsx
@@ -648,7 +648,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PRAP_NewApp_Development_Plan_v1.10.xlsx - the approved baseline, Gate N1 closed 2026-08-13</t>
+          <t>PRAP_NewApp_Development_Plan_v1.11.xlsx - the approved baseline, Gate N1 closed 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>The NR-ids are READ from PRAP_NewApp_Development_Plan_v1.10.xlsx when this workbook is generated, not re-typed. A requirement cannot be dropped between the two documents without this sheet showing it.</t>
+          <t>The NR-ids are READ from PRAP_NewApp_Development_Plan_v1.11.xlsx when this workbook is generated, not re-typed. A requirement cannot be dropped between the two documents without this sheet showing it.</t>
         </is>
       </c>
     </row>
